--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3629-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3629-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B7C8FA8-8EB7-4185-B899-D23EABDBDB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C13C809D-7AAD-4CE4-B391-223683689554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{809F5A34-6AAA-4CAC-BA11-13598FC8A521}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{3418D573-8DDA-4CDC-9EC9-61A29DB183A6}"/>
   </bookViews>
   <sheets>
     <sheet name="3629-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,30 +1451,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0AF940-628D-453C-B949-CBA38F0ADAC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F17C8A-351B-4D3D-940D-DE6BDB9A1600}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1664,7 +1664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2021</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2020</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>29</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2019</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2018</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2017</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2016</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2015</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2014</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2013</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2012</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2011</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2010</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2009</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2008</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
         <v>38</v>
       </c>
